--- a/request-folder/정보보호_2팀_9012/신청.xlsx
+++ b/request-folder/정보보호_2팀_9012/신청.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M3"/>
+  <dimension ref="B1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -451,55 +451,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>대상방화벽</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>출발지IP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>출발지</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>목적지IP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>목적지</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>프로토콜</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>포트</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>방향</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>용도</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>시작일</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>종료일</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -511,55 +516,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>SECUI-FW-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>10.10.40.7</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>관리PC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>172.16.1.20</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>관리시스템</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>SSH 관리 접근</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>한시 신청</t>
         </is>
@@ -571,55 +581,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>SECUI-FW-01;SECUI-FW-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>10.10.50.1;10.10.50.2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>관리PC군</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>10.20.20.9</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>DMZ관리</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>OUT</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>DMZ 관리 콘솔</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>다중주소</t>
         </is>
